--- a/public/exports-60-250-with-coowners/29189714.xlsx
+++ b/public/exports-60-250-with-coowners/29189714.xlsx
@@ -4939,12 +4939,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283771</t>
+          <t xml:space="preserve">311283774</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283776</t>
+          <t xml:space="preserve">311283775</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
